--- a/Statistic_Inflatio_Russia.xlsx
+++ b/Statistic_Inflatio_Russia.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ugin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ugin\Desktop\пр 11\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAA76E9F-9A8E-4A7C-BA8E-9925CA370A44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90A5823E-D348-4DD0-B2AE-F8D2CDFE3E5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2295" yWindow="2295" windowWidth="21375" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3330" yWindow="3330" windowWidth="21375" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Инфляция_Год_к_Году" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="15">
   <si>
     <t>Год</t>
   </si>
@@ -63,6 +63,9 @@
   </si>
   <si>
     <t>Всего</t>
+  </si>
+  <si>
+    <t>Year</t>
   </si>
 </sst>
 </file>
@@ -447,7 +450,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
